--- a/data/trans_orig/IP07C18-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C18-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41126</t>
+          <t>41385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65780</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86817</t>
+          <t>86682</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>64600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86666</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136806</t>
+          <t>136083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166781</t>
+          <t>168272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67116</t>
+          <t>67287</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88610</t>
+          <t>89265</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75295</t>
+          <t>73557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97986</t>
+          <t>97765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147042</t>
+          <t>148500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>179595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>36238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55975</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64194</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89261</t>
+          <t>89347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52779</t>
+          <t>52290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24066</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29319</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44572</t>
+          <t>45692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>107153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95034</t>
+          <t>95579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>123528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211492</t>
+          <t>211827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249283</t>
+          <t>248763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101109</t>
+          <t>102148</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127511</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108062</t>
+          <t>107611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135311</t>
+          <t>134636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>215970</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>255334</t>
+          <t>253998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72002</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117433</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>36934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29008</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45839</t>
+          <t>47016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61969</t>
+          <t>63049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>33592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94806</t>
+          <t>94927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117915</t>
+          <t>117263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101867</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127124</t>
+          <t>126869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205283</t>
+          <t>203461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240023</t>
+          <t>239692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,64%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55566</t>
+          <t>56962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78098</t>
+          <t>78919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65001</t>
+          <t>63804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88696</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125406</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158902</t>
+          <t>160040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32483</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52694</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42838</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58248</t>
+          <t>58813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75403</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44986</t>
+          <t>45389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159797</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188713</t>
+          <t>189272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153968</t>
+          <t>153186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185066</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>322703</t>
+          <t>321517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>364618</t>
+          <t>363346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107695</t>
+          <t>106827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186192</t>
+          <t>188936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>227435</t>
+          <t>227984</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21277</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36298</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33805</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,82 +6891,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8815</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>9602</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>15941</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4274</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8243</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>9602</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>5649</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>14844</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106551</t>
+          <t>107120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131443</t>
+          <t>132834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95158</t>
+          <t>95331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121273</t>
+          <t>122683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209748</t>
+          <t>209134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246587</t>
+          <t>245768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82791</t>
+          <t>83843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108874</t>
+          <t>108713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75610</t>
+          <t>74569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101501</t>
+          <t>100746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166784</t>
+          <t>166909</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202484</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>40878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40293</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>62682</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47208</t>
+          <t>47249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30114</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44724</t>
+          <t>45828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67757</t>
+          <t>68345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87792</t>
+          <t>88434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61638</t>
+          <t>60642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>158796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190111</t>
+          <t>189840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>146506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>177312</t>
+          <t>178418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>314395</t>
+          <t>316591</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>361213</t>
+          <t>359336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>143664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>118900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148280</t>
+          <t>147762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>241557</t>
+          <t>239399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283297</t>
+          <t>280912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>85692</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
